--- a/main/java/hospitaldatabase/patientdetail.xlsx
+++ b/main/java/hospitaldatabase/patientdetail.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>FirstName</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>SIMON</t>
+  </si>
+  <si>
+    <t>johnson</t>
   </si>
 </sst>
 </file>
@@ -168,7 +171,7 @@
         <v>23.0</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>14</v>
@@ -203,7 +206,7 @@
         <v>14</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>251.02</v>
+        <v>250.01</v>
       </c>
     </row>
   </sheetData>
